--- a/CardArchive/Tools/DataExport/Club.xlsx
+++ b/CardArchive/Tools/DataExport/Club.xlsx
@@ -8,6 +8,44 @@
     <sheet name="Club" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -71,37 +109,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
@@ -171,12 +209,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">synergy_threshold</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">!String</t>
+          <t xml:space="preserve">!Int</t>
         </is>
       </c>
       <c r="E8"/>
@@ -185,7 +223,64 @@
     </row>
     <row r="9">
       <c r="A9"/>
-      <c r="B9" t="inlineStr">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">synergy_type</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClubSynergyType</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">synergy_value</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndTable</t>
         </is>
@@ -239,10 +334,25 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">synergy_threshold</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">synergy_type</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">synergy_value</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
@@ -269,6 +379,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClubSynergyType</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t xml:space="preserve">!String</t>
         </is>
       </c>
@@ -288,7 +413,18 @@
         </is>
       </c>
       <c r="F4"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">방과후 디저트부</t>
         </is>
@@ -309,7 +445,18 @@
         </is>
       </c>
       <c r="F5"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">아리우스 스쿼드</t>
         </is>
@@ -334,7 +481,18 @@
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Millenium/Engineering_Department_Icon.png</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">엔지니어부</t>
         </is>
@@ -355,7 +513,18 @@
         </is>
       </c>
       <c r="F7"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">미식연구회</t>
         </is>
@@ -380,7 +549,18 @@
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Gehenna/Hot_Sprint_Deparment_Icon.png</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">온천개발부</t>
         </is>
@@ -401,7 +581,18 @@
         </is>
       </c>
       <c r="F9"/>
-      <c r="G9" t="inlineStr">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">정의실현부</t>
         </is>
@@ -422,7 +613,18 @@
         </is>
       </c>
       <c r="F10"/>
-      <c r="G10" t="inlineStr">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">보충수업부</t>
         </is>
@@ -439,7 +641,18 @@
       </c>
       <c r="E11"/>
       <c r="F11"/>
-      <c r="G11" t="inlineStr">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">RABBIT 소대</t>
         </is>
@@ -460,7 +673,18 @@
         </is>
       </c>
       <c r="F12"/>
-      <c r="G12" t="inlineStr">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">급양부</t>
         </is>
@@ -481,7 +705,18 @@
         </is>
       </c>
       <c r="F13"/>
-      <c r="G13" t="inlineStr">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">티파티</t>
         </is>
@@ -506,7 +741,18 @@
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Trinity/Trinity_Vigilante_Crew_Icon.png</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">트리니티 자경단</t>
         </is>
